--- a/Results/MorphologyResults/StatisticalResults.xlsx
+++ b/Results/MorphologyResults/StatisticalResults.xlsx
@@ -70,13 +70,13 @@
     <t xml:space="preserve">adj.p.value</t>
   </si>
   <si>
+    <t xml:space="preserve">Mathers-Strawberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prasiola-Strawberry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prasiola-Mathers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strawberry-Mathers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strawberry-Prasiola</t>
   </si>
 </sst>
 </file>
@@ -439,7 +439,7 @@
         <v>0.443324071981843</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1639493282282</v>
+        <v>8.16394932822818</v>
       </c>
       <c r="E2" t="n">
         <v>6</v>
@@ -448,7 +448,7 @@
         <v>172</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000000890896123889581</v>
+        <v>0.0000000890896123889611</v>
       </c>
     </row>
     <row r="3">
@@ -503,16 +503,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0606401593889158</v>
+        <v>0.0606401593889156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0303200796944579</v>
+        <v>0.0303200796944578</v>
       </c>
       <c r="E2" t="n">
         <v>11.2469250597407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000452516438927288</v>
+        <v>0.0000452516438927299</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>0.23453938915804</v>
+        <v>0.234539389158039</v>
       </c>
       <c r="D3" t="n">
         <v>0.00269585504779356</v>
@@ -573,7 +573,7 @@
         <v>0.00311173139341711</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00155586569670855</v>
+        <v>0.00155586569670856</v>
       </c>
       <c r="E2" t="n">
         <v>1.01686511422261</v>
@@ -637,7 +637,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0226695500420342</v>
+        <v>0.0226695500420341</v>
       </c>
       <c r="D2" t="n">
         <v>0.0113347750210171</v>
@@ -646,7 +646,7 @@
         <v>11.9173307821831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000266501041784522</v>
+        <v>0.0000266501041784524</v>
       </c>
     </row>
     <row r="3">
@@ -710,16 +710,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0574118125012742</v>
+        <v>-0.00504326040460569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0254452270949172</v>
+        <v>-0.0370098458109627</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0893783979076311</v>
+        <v>0.0269233250017513</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000139390236017722</v>
+        <v>0.925028828596805</v>
       </c>
     </row>
     <row r="3">
@@ -733,16 +733,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00504326040460578</v>
+        <v>0.0523685520966682</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0269233250017512</v>
+        <v>0.0204019666903112</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0370098458109628</v>
+        <v>0.0843351375030252</v>
       </c>
       <c r="G3" t="n">
-        <v>0.925028828596803</v>
+        <v>0.000537449521241795</v>
       </c>
     </row>
     <row r="4">
@@ -756,16 +756,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0523685520966684</v>
+        <v>0.0574118125012739</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0843351375030254</v>
+        <v>0.0254452270949169</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0204019666903114</v>
+        <v>0.0893783979076309</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000537449521241906</v>
+        <v>0.000139390236017611</v>
       </c>
     </row>
   </sheetData>
@@ -813,16 +813,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00999664311876288</v>
+        <v>-0.027536703365594</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02898401844041</v>
+        <v>-0.0465240786872411</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00899073220288418</v>
+        <v>-0.00854932804394695</v>
       </c>
       <c r="G2" t="n">
-        <v>0.424195648225779</v>
+        <v>0.002410714136871</v>
       </c>
     </row>
     <row r="3">
@@ -836,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.027536703365594</v>
+        <v>-0.0375333464843569</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00854932804394697</v>
+        <v>-0.056520721806004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0465240786872411</v>
+        <v>-0.0185459711627098</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002410714136871</v>
+        <v>0.0000271738195394278</v>
       </c>
     </row>
     <row r="4">
@@ -859,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0375333464843569</v>
+        <v>-0.00999664311876288</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0185459711627099</v>
+        <v>-0.0289840184404099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.056520721806004</v>
+        <v>0.00899073220288419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000271738195394278</v>
+        <v>0.424195648225779</v>
       </c>
     </row>
   </sheetData>

--- a/Results/MorphologyResults/StatisticalResults.xlsx
+++ b/Results/MorphologyResults/StatisticalResults.xlsx
@@ -6,15 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Locality_Omnibus" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Locality_Pairwise" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Predation_Omnibus" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Two-factor ANOVA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -43,34 +41,16 @@
     <t xml:space="preserve">location</t>
   </si>
   <si>
+    <t xml:space="preserve">repairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location:repairs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Residuals</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">locality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCL (95%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr &gt; d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathers:Prasiola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathers:Strawberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prasiola:Strawberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repairs</t>
   </si>
 </sst>
 </file>
@@ -442,10 +422,10 @@
         <v>0.11458966255061</v>
       </c>
       <c r="F2" t="n">
-        <v>5.62976295861969</v>
+        <v>5.60682178731661</v>
       </c>
       <c r="G2" t="n">
-        <v>4.07055263246715</v>
+        <v>4.04381784540784</v>
       </c>
       <c r="H2" t="n">
         <v>0.001</v>
@@ -456,214 +436,88 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.794662268614288</v>
+        <v>0.0116086700006441</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00913404906453204</v>
+        <v>0.0116086700006441</v>
       </c>
       <c r="E3" t="n">
-        <v>0.88541033744939</v>
-      </c>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+        <v>0.0129343456063821</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.26574368291759</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.743784420184933</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.222</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0126541147257249</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.00632705736286244</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0140991770113419</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.689866529762325</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.81328969219977</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.797</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.770399483887919</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00917142242723713</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.858376814831666</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="n">
         <v>89</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C6" t="n">
         <v>0.897507330785722</v>
       </c>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.0641364580971953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0371228058375216</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3.37201685056743</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.0371158267949503</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0368623661490656</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.65061605927327</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0692346471155692</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0379052915737663</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.86508690545347</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.017758752447841</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.017758752447841</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0197867491871003</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.77638276877078</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.34481105571092</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.089</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="n">
-        <v>88</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.879748578337881</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.00999714293565774</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9802132508129</v>
-      </c>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.897507330785722</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
